--- a/benchmark_CSP/CSP_Benchmark_Validation_Results.xlsx
+++ b/benchmark_CSP/CSP_Benchmark_Validation_Results.xlsx
@@ -2,15 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\4900063\Work\SCIENCE\papers\optimization_1\COMPUTATIONAL_EXPERIMENTS\benchmark_CSP_Sun2022\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1792368D-4F45-4966-92A7-1530708D98CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C25F46-FB9B-4BD8-89B5-8DA9A9724E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43215" yWindow="2685" windowWidth="31770" windowHeight="16905" xr2:uid="{088AB062-1B41-4D05-842F-B9E6480BAF0B}"/>
+    <workbookView xWindow="40785" yWindow="2235" windowWidth="31770" windowHeight="16905" xr2:uid="{088AB062-1B41-4D05-842F-B9E6480BAF0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7801,6 +7796,7 @@
   </sheetData>
   <autoFilter ref="A1:G282" xr:uid="{EA5C3D4D-1D42-4B6D-8700-BCFE72294B28}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;G</oddHeader>
   </headerFooter>
